--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>16.39997</v>
+      </c>
+      <c r="E4" t="n">
         <v>16.56624</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.39997</v>
       </c>
       <c r="F4" t="n">
         <v>42.04931</v>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>16.50378</v>
+      </c>
+      <c r="D8" t="n">
         <v>16.39389</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>16.44731</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16.50378</v>
       </c>
       <c r="F8" t="n">
         <v>42.68588</v>
@@ -641,10 +641,10 @@
         <v>16.66972</v>
       </c>
       <c r="D9" t="n">
+        <v>16.55026</v>
+      </c>
+      <c r="E9" t="n">
         <v>16.66928</v>
-      </c>
-      <c r="E9" t="n">
-        <v>16.55026</v>
       </c>
       <c r="F9" t="n">
         <v>41.86002</v>
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.66496</v>
+        <v>16.73422</v>
       </c>
       <c r="D10" t="n">
         <v>16.4006</v>
       </c>
       <c r="E10" t="n">
-        <v>16.73422</v>
+        <v>16.66496</v>
       </c>
       <c r="F10" t="n">
         <v>42.75918</v>
